--- a/cl_st1_ph1_andrea/corpus/00_sources/tv_commercials.xlsx
+++ b/cl_st1_ph1_andrea/corpus/00_sources/tv_commercials.xlsx
@@ -23863,7 +23863,11 @@
           <t>https://youtu.be/zNs4DQB7nDU</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr"/>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>0:00:00</t>
+        </is>
+      </c>
       <c r="I460" t="inlineStr">
         <is>
           <t>0:00:35</t>

--- a/cl_st1_ph1_andrea/corpus/00_sources/tv_commercials.xlsx
+++ b/cl_st1_ph1_andrea/corpus/00_sources/tv_commercials.xlsx
@@ -38094,7 +38094,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>0:00:59</t>
+          <t>0:00:00</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">

--- a/cl_st1_ph1_andrea/corpus/00_sources/tv_commercials.xlsx
+++ b/cl_st1_ph1_andrea/corpus/00_sources/tv_commercials.xlsx
@@ -38099,7 +38099,7 @@
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>0:00:30</t>
+          <t>0:00:59</t>
         </is>
       </c>
       <c r="J739" t="b">

--- a/cl_st1_ph1_andrea/corpus/00_sources/tv_commercials.xlsx
+++ b/cl_st1_ph1_andrea/corpus/00_sources/tv_commercials.xlsx
@@ -43314,10 +43314,8 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" t="inlineStr">
-        <is>
-          <t>2020-26</t>
-        </is>
+      <c r="A842" t="n">
+        <v>2020</v>
       </c>
       <c r="B842" t="n">
         <v>1</v>
@@ -43334,7 +43332,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>tv_com_2020-26_1</t>
+          <t>tv_com_2020_1</t>
         </is>
       </c>
       <c r="F842" t="inlineStr">

--- a/cl_st1_ph1_andrea/corpus/00_sources/tv_commercials.xlsx
+++ b/cl_st1_ph1_andrea/corpus/00_sources/tv_commercials.xlsx
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services, Consumer Goods &amp; Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services, Consumer Goods &amp; Services</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services, Consumer Goods &amp; Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services, Consumer Goods &amp; Services</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -17182,7 +17182,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -17482,7 +17482,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -17842,7 +17842,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -18622,7 +18622,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -18682,7 +18682,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -19222,7 +19222,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -19582,7 +19582,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -20062,7 +20062,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -20242,7 +20242,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -24202,7 +24202,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -24262,7 +24262,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -25942,7 +25942,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -26782,7 +26782,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -26842,7 +26842,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -26902,7 +26902,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -27202,7 +27202,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -27322,7 +27322,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -27500,7 +27500,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -27560,7 +27560,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -27620,7 +27620,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -27680,7 +27680,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -27800,7 +27800,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services, Fashion &amp; Consumer Goods</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services, Fashion &amp; Consumer Goods</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -29180,7 +29180,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -29240,7 +29240,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -29360,7 +29360,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -29480,7 +29480,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -29720,7 +29720,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -29780,7 +29780,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -29840,7 +29840,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -29960,7 +29960,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -30140,7 +30140,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -30320,7 +30320,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -30380,7 +30380,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -30440,7 +30440,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -30560,7 +30560,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -30680,7 +30680,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -30800,7 +30800,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -30860,7 +30860,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -30920,7 +30920,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -30980,7 +30980,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -31040,7 +31040,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -31280,7 +31280,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -31580,7 +31580,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -31640,7 +31640,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -31760,7 +31760,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -31820,7 +31820,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -31880,7 +31880,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -32000,7 +32000,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -32060,7 +32060,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -32120,7 +32120,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -32180,7 +32180,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -32300,7 +32300,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -32360,7 +32360,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -32420,7 +32420,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -32480,7 +32480,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -32900,7 +32900,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -32960,7 +32960,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -33020,7 +33020,7 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -33260,7 +33260,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -33380,7 +33380,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -33500,7 +33500,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -33620,7 +33620,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -33740,7 +33740,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -34280,7 +34280,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -34340,7 +34340,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -34400,7 +34400,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -34520,7 +34520,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -34580,7 +34580,7 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -34640,7 +34640,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -34880,7 +34880,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
@@ -35300,7 +35300,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -35360,7 +35360,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -36500,7 +36500,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -36560,7 +36560,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -36620,7 +36620,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
@@ -36680,7 +36680,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -36740,7 +36740,7 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -36800,7 +36800,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -36860,7 +36860,7 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
@@ -36920,7 +36920,7 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -36980,7 +36980,7 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
@@ -37040,7 +37040,7 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
@@ -37220,7 +37220,7 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -37280,7 +37280,7 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -37340,7 +37340,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -37400,7 +37400,7 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -37460,7 +37460,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -37520,7 +37520,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -37640,7 +37640,7 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
@@ -37700,7 +37700,7 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -37760,7 +37760,7 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
@@ -37880,7 +37880,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -37940,7 +37940,7 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
@@ -38000,7 +38000,7 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -38060,7 +38060,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -38120,7 +38120,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -38180,7 +38180,7 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -38240,7 +38240,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -38300,7 +38300,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -38360,7 +38360,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
@@ -38420,7 +38420,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -38480,7 +38480,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -38540,7 +38540,7 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
@@ -38600,7 +38600,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -38660,7 +38660,7 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
@@ -38720,7 +38720,7 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
@@ -38780,7 +38780,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -38840,7 +38840,7 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
@@ -38900,7 +38900,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -38960,7 +38960,7 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
@@ -39080,7 +39080,7 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
@@ -39140,7 +39140,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
@@ -39260,7 +39260,7 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
@@ -39320,7 +39320,7 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
@@ -39380,7 +39380,7 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
@@ -39440,7 +39440,7 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
@@ -39500,7 +39500,7 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -39560,7 +39560,7 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -39620,7 +39620,7 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -39680,7 +39680,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -39740,7 +39740,7 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
@@ -39800,7 +39800,7 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
@@ -39860,7 +39860,7 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -39920,7 +39920,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -39980,7 +39980,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -40040,7 +40040,7 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
@@ -42860,7 +42860,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Transport (Personal/ Public), Travel &amp; Energy</t>
+          <t>Transport (Personal &amp; Public), Travel &amp; Energy</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
@@ -43700,7 +43700,7 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
@@ -43760,7 +43760,7 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
@@ -43820,7 +43820,7 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
@@ -43880,7 +43880,7 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
@@ -43940,7 +43940,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
@@ -44180,7 +44180,7 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
@@ -44240,7 +44240,7 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
@@ -44300,7 +44300,7 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
@@ -44480,7 +44480,7 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -44540,7 +44540,7 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
@@ -44720,7 +44720,7 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
@@ -44780,7 +44780,7 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
@@ -44840,7 +44840,7 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
@@ -44960,7 +44960,7 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
@@ -45320,7 +45320,7 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
@@ -45680,7 +45680,7 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
@@ -45740,7 +45740,7 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
@@ -45800,7 +45800,7 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
@@ -45920,7 +45920,7 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
@@ -45980,7 +45980,7 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
@@ -46100,7 +46100,7 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
@@ -46160,7 +46160,7 @@
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
@@ -46220,7 +46220,7 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
@@ -46280,7 +46280,7 @@
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
@@ -46340,7 +46340,7 @@
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
@@ -46400,7 +46400,7 @@
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
@@ -46460,7 +46460,7 @@
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
@@ -46520,7 +46520,7 @@
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
@@ -46640,7 +46640,7 @@
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
@@ -46700,7 +46700,7 @@
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
@@ -46760,7 +46760,7 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
@@ -46880,7 +46880,7 @@
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
@@ -46940,7 +46940,7 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
@@ -47060,7 +47060,7 @@
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
@@ -47120,7 +47120,7 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
@@ -47180,7 +47180,7 @@
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
@@ -47360,7 +47360,7 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
@@ -47420,7 +47420,7 @@
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
@@ -47480,7 +47480,7 @@
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
@@ -47540,7 +47540,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
@@ -47600,7 +47600,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
@@ -47660,7 +47660,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -47720,7 +47720,7 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retail (Fashion/ Consumer Goods) &amp;  Services </t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -47780,7 +47780,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
@@ -47840,7 +47840,7 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
@@ -47900,7 +47900,7 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
@@ -47960,7 +47960,7 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
@@ -48080,7 +48080,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
@@ -48260,7 +48260,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
@@ -48380,7 +48380,7 @@
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
@@ -48560,7 +48560,7 @@
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
@@ -48680,7 +48680,7 @@
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
@@ -48740,7 +48740,7 @@
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
@@ -48860,7 +48860,7 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
@@ -49040,7 +49040,7 @@
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
@@ -49100,7 +49100,7 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
@@ -49160,7 +49160,7 @@
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
@@ -49280,7 +49280,7 @@
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -49580,7 +49580,7 @@
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
@@ -50900,7 +50900,7 @@
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
@@ -51200,7 +51200,7 @@
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
@@ -51260,7 +51260,7 @@
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
@@ -51320,7 +51320,7 @@
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
@@ -51380,7 +51380,7 @@
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
@@ -51440,7 +51440,7 @@
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
@@ -51500,7 +51500,7 @@
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
@@ -51620,7 +51620,7 @@
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
@@ -51680,7 +51680,7 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
@@ -51860,7 +51860,7 @@
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
@@ -51920,7 +51920,7 @@
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
@@ -51980,7 +51980,7 @@
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
@@ -52220,7 +52220,7 @@
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
@@ -52280,7 +52280,7 @@
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
@@ -52400,7 +52400,7 @@
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
@@ -52760,7 +52760,7 @@
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
@@ -52940,7 +52940,7 @@
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
@@ -53000,7 +53000,7 @@
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
@@ -53060,7 +53060,7 @@
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
@@ -53120,7 +53120,7 @@
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
@@ -53180,7 +53180,7 @@
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
@@ -53240,7 +53240,7 @@
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
@@ -53360,7 +53360,7 @@
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E883" t="inlineStr">
@@ -53420,7 +53420,7 @@
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
@@ -53720,7 +53720,7 @@
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
@@ -53780,7 +53780,7 @@
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
@@ -53960,7 +53960,7 @@
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E893" t="inlineStr">
@@ -54080,7 +54080,7 @@
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
@@ -54200,7 +54200,7 @@
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
@@ -54740,7 +54740,7 @@
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
@@ -54800,7 +54800,7 @@
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
@@ -54860,7 +54860,7 @@
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
@@ -54920,7 +54920,7 @@
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
@@ -54980,7 +54980,7 @@
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
@@ -55040,7 +55040,7 @@
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
@@ -55100,7 +55100,7 @@
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
@@ -55160,7 +55160,7 @@
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
@@ -55220,7 +55220,7 @@
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
@@ -55400,7 +55400,7 @@
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -55460,7 +55460,7 @@
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
@@ -55580,7 +55580,7 @@
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -55700,7 +55700,7 @@
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
@@ -55760,7 +55760,7 @@
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
@@ -55940,7 +55940,7 @@
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -56060,7 +56060,7 @@
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -56180,7 +56180,7 @@
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Nutrition</t>
+          <t>Food, Beverages &amp; Nutrition</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
@@ -56240,7 +56240,7 @@
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
@@ -56360,7 +56360,7 @@
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -56420,7 +56420,7 @@
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -56480,7 +56480,7 @@
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -56540,7 +56540,7 @@
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>Retail (Fashion/ Consumer Goods) &amp;  Services</t>
+          <t>Retail (Fashion &amp; Consumer Goods) &amp; Services</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
@@ -56780,7 +56780,7 @@
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
@@ -57080,7 +57080,7 @@
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
@@ -57140,7 +57140,7 @@
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
@@ -57200,7 +57200,7 @@
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
@@ -57320,7 +57320,7 @@
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
@@ -57560,7 +57560,7 @@
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
@@ -57680,7 +57680,7 @@
       </c>
       <c r="D955" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E955" t="inlineStr">
@@ -57740,7 +57740,7 @@
       </c>
       <c r="D956" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E956" t="inlineStr">
@@ -57800,7 +57800,7 @@
       </c>
       <c r="D957" t="inlineStr">
         <is>
-          <t>Technology, Communication &amp; Eletronics</t>
+          <t>Technology, Communication &amp; Electronics</t>
         </is>
       </c>
       <c r="E957" t="inlineStr">
